--- a/artfynd/Gåsselmyran artfynd.xlsx
+++ b/artfynd/Gåsselmyran artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104220698</v>
+        <v>76303209</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gåsselåsen, Ång</t>
+          <t>Gåsseliden, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>683803</v>
+        <v>682627</v>
       </c>
       <c r="R2" t="n">
-        <v>7101645</v>
+        <v>7101611</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2018-08-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2018-08-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,57 +760,61 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104230290</v>
+        <v>111835736</v>
       </c>
       <c r="B3" t="n">
-        <v>92535</v>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gåsselliden, Bjurholm, Ång</t>
+          <t>Gåsselliden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>682592</v>
+        <v>682650</v>
       </c>
       <c r="R3" t="n">
-        <v>7101488</v>
+        <v>7101507</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,61 +861,61 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104220660</v>
+        <v>76303210</v>
       </c>
       <c r="B4" t="n">
-        <v>90283</v>
+        <v>92083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1962</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gåsselåsen, Ång</t>
+          <t>Gåsseliden, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>682614</v>
+        <v>682627</v>
       </c>
       <c r="R4" t="n">
-        <v>7101484</v>
+        <v>7101611</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -938,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2018-08-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2018-08-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -958,22 +962,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126840197</v>
+        <v>104220660</v>
       </c>
       <c r="B5" t="n">
-        <v>78738</v>
+        <v>90932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,40 +989,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gåsselmyren, Ång</t>
+          <t>Gåsselåsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683074</v>
+        <v>682614</v>
       </c>
       <c r="R5" t="n">
-        <v>7101349</v>
+        <v>7101484</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1038,12 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1052,37 +1057,32 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, kristina stenmarck, Jennica Andersson, Isac Enetjärn, Elke Blöhbaum, Lise Mortensen, Lisa Requin, Maria  Persbo , Vilhelm Kroon, Eleonor Johansson, Hedda Bring, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Lotta Ihse</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104220674</v>
+        <v>104220673</v>
       </c>
       <c r="B6" t="n">
-        <v>92551</v>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>682951</v>
+        <v>682597</v>
       </c>
       <c r="R6" t="n">
-        <v>7101573</v>
+        <v>7101488</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,48 +1172,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126839045</v>
+        <v>111835733</v>
       </c>
       <c r="B7" t="n">
-        <v>78647</v>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gåsselmyran, Ång</t>
+          <t>Gåsselliden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>683033</v>
+        <v>682486</v>
       </c>
       <c r="R7" t="n">
-        <v>7101459</v>
+        <v>7101355</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,61 +1257,61 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104220705</v>
+        <v>111835738</v>
       </c>
       <c r="B8" t="n">
-        <v>92535</v>
+        <v>91962</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gåsselåsen, Ång</t>
+          <t>Gåsselliden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>682741</v>
+        <v>682489</v>
       </c>
       <c r="R8" t="n">
-        <v>7101486</v>
+        <v>7101344</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1358,22 +1358,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104220658</v>
+        <v>111835730</v>
       </c>
       <c r="B9" t="n">
-        <v>90283</v>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,34 +1385,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gåsselåsen, Ång</t>
+          <t>Gåsselliden, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>682846</v>
+        <v>682478</v>
       </c>
       <c r="R9" t="n">
-        <v>7101291</v>
+        <v>7101357</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,12 +1439,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1455,22 +1459,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104230288</v>
+        <v>111835732</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>93191</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,34 +1486,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gåsselliden, Bjurholm, Ång</t>
+          <t>Gåsselliden, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>682650</v>
+        <v>682486</v>
       </c>
       <c r="R10" t="n">
-        <v>7101462</v>
+        <v>7101355</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,12 +1540,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1548,45 +1556,30 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104220714</v>
+        <v>104230290</v>
       </c>
       <c r="B11" t="n">
-        <v>78386</v>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,34 +1587,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gåsselåsen, Ång</t>
+          <t>Gåsselliden, Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>682901</v>
+        <v>682592</v>
       </c>
       <c r="R11" t="n">
-        <v>7101266</v>
+        <v>7101488</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,22 +1661,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Carl Jansson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111835730</v>
+        <v>111835731</v>
       </c>
       <c r="B12" t="n">
-        <v>92527</v>
+        <v>93235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,21 +1688,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1778,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126835887</v>
+        <v>104230288</v>
       </c>
       <c r="B13" t="n">
-        <v>91406</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,34 +1789,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Gåsselliden, Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>683085</v>
+        <v>682650</v>
       </c>
       <c r="R13" t="n">
-        <v>7101428</v>
+        <v>7101462</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1846,12 +1843,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1886,17 +1883,21 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carl Jansson, kristina stenmarck, Jennica Andersson, Isac Enetjärn, Beke Regelin, Elke Blöhbaum, Lise Mortensen, Lisa Requin, Peter Andersson, Maria  Persbo , Vilhelm Kroon, Eleonor Johansson, Hedda Bring, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Carl Jansson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>16846942</v>
+        <v>111835737</v>
       </c>
       <c r="B14" t="n">
-        <v>78738</v>
+        <v>79917</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1904,34 +1905,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gåsselmyran, Ång</t>
+          <t>Gåsselliden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>683144</v>
+        <v>682659</v>
       </c>
       <c r="R14" t="n">
-        <v>7101221</v>
+        <v>7101502</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1958,12 +1959,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2013-06-30</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2013-06-30</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1974,26 +1975,16 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>brandhögstubbe tall</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Niina Sallmén, sofia nordin</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2004,45 +1995,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104220706</v>
+        <v>126835882</v>
       </c>
       <c r="B15" t="n">
-        <v>92535</v>
+        <v>78993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gåsselåsen, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>683198</v>
+        <v>683072</v>
       </c>
       <c r="R15" t="n">
-        <v>7101382</v>
+        <v>7101304</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2069,12 +2060,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2085,26 +2076,41 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson</t>
+          <t>Carl Jansson, kristina stenmarck, Jennica Andersson, Isac Enetjärn, Beke Regelin, Elke Blöhbaum, Lise Mortensen, Lisa Requin, Peter Andersson, Maria  Persbo , Vilhelm Kroon, Eleonor Johansson, Hedda Bring, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104220661</v>
+        <v>126839045</v>
       </c>
       <c r="B16" t="n">
-        <v>90283</v>
+        <v>78993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2112,37 +2118,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gåsselåsen, Ång</t>
+          <t>Gåsselmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>682990</v>
+        <v>683033</v>
       </c>
       <c r="R16" t="n">
-        <v>7101559</v>
+        <v>7101459</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2166,12 +2172,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2186,22 +2192,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104230293</v>
+        <v>126840199</v>
       </c>
       <c r="B17" t="n">
-        <v>78738</v>
+        <v>78993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2209,37 +2219,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gåsselliden, Bjurholm, Ång</t>
+          <t>Gåsselmyren, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>683027</v>
+        <v>683074</v>
       </c>
       <c r="R17" t="n">
-        <v>7101473</v>
+        <v>7101300</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2263,12 +2276,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gammal silverlåga med brandljud och kol på undersidan</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2277,88 +2295,71 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström</t>
+          <t>Beke Regelin, Carl Jansson, kristina stenmarck, Jennica Andersson, Isac Enetjärn, Elke Blöhbaum, Lise Mortensen, Lisa Requin, Maria  Persbo , Vilhelm Kroon, Eleonor Johansson, Hedda Bring, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126840198</v>
+        <v>126835887</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>92083</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gåsselmyren, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>683072</v>
+        <v>683085</v>
       </c>
       <c r="R18" t="n">
-        <v>7101302</v>
+        <v>7101428</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2390,79 +2391,84 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Många på tallstammarna</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, kristina stenmarck, Jennica Andersson, Isac Enetjärn, Elke Blöhbaum, Lise Mortensen, Lisa Requin, Maria  Persbo , Vilhelm Kroon, Eleonor Johansson, Hedda Bring, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Lotta Ihse</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Carl Jansson, kristina stenmarck, Jennica Andersson, Isac Enetjärn, Beke Regelin, Elke Blöhbaum, Lise Mortensen, Lisa Requin, Peter Andersson, Maria  Persbo , Vilhelm Kroon, Eleonor Johansson, Hedda Bring, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104230294</v>
+        <v>104220658</v>
       </c>
       <c r="B19" t="n">
-        <v>92519</v>
+        <v>90932</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6055</v>
+        <v>1962</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gåsselliden, Bjurholm, Ång</t>
+          <t>Gåsselåsen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>683077</v>
+        <v>682846</v>
       </c>
       <c r="R19" t="n">
-        <v>7101489</v>
+        <v>7101291</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2509,48 +2515,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104220694</v>
+        <v>104220661</v>
       </c>
       <c r="B20" t="n">
-        <v>91406</v>
+        <v>90932</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1503</v>
+        <v>1962</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,10 +2562,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>683606</v>
+        <v>682990</v>
       </c>
       <c r="R20" t="n">
-        <v>7101466</v>
+        <v>7101559</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,10 +2624,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104220664</v>
+        <v>104220662</v>
       </c>
       <c r="B21" t="n">
-        <v>90283</v>
+        <v>90932</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2657,10 +2659,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>683133</v>
+        <v>683114</v>
       </c>
       <c r="R21" t="n">
-        <v>7101365</v>
+        <v>7101481</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2719,10 +2721,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111835731</v>
+        <v>104220664</v>
       </c>
       <c r="B22" t="n">
-        <v>92571</v>
+        <v>90932</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2730,34 +2732,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>1962</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gåsselliden, Ång</t>
+          <t>Gåsselåsen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>682478</v>
+        <v>683133</v>
       </c>
       <c r="R22" t="n">
-        <v>7101357</v>
+        <v>7101365</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2784,12 +2786,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2804,26 +2806,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104230302</v>
+        <v>104230286</v>
       </c>
       <c r="B23" t="n">
-        <v>90283</v>
+        <v>90932</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2855,10 +2853,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>683132</v>
+        <v>682781</v>
       </c>
       <c r="R23" t="n">
-        <v>7101470</v>
+        <v>7101323</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2936,10 +2934,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104230300</v>
+        <v>104230295</v>
       </c>
       <c r="B24" t="n">
-        <v>90283</v>
+        <v>90932</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2971,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>683099</v>
+        <v>683077</v>
       </c>
       <c r="R24" t="n">
-        <v>7101481</v>
+        <v>7101491</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3052,10 +3050,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111835738</v>
+        <v>104230296</v>
       </c>
       <c r="B25" t="n">
-        <v>92727</v>
+        <v>90932</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3063,34 +3061,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gåsselliden, Ång</t>
+          <t>Gåsselliden, Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>682489</v>
+        <v>683082</v>
       </c>
       <c r="R25" t="n">
-        <v>7101344</v>
+        <v>7101488</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3117,12 +3115,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3133,30 +3131,45 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Carl Jansson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111835733</v>
+        <v>104230300</v>
       </c>
       <c r="B26" t="n">
-        <v>92551</v>
+        <v>90932</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3164,34 +3177,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gåsselliden, Ång</t>
+          <t>Gåsselliden, Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>682486</v>
+        <v>683099</v>
       </c>
       <c r="R26" t="n">
-        <v>7101355</v>
+        <v>7101481</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3218,12 +3231,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3234,30 +3247,45 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Carl Jansson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111835732</v>
+        <v>104230302</v>
       </c>
       <c r="B27" t="n">
-        <v>92529</v>
+        <v>90932</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3265,34 +3293,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gåsselliden, Ång</t>
+          <t>Gåsselliden, Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>682486</v>
+        <v>683132</v>
       </c>
       <c r="R27" t="n">
-        <v>7101355</v>
+        <v>7101470</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3319,12 +3347,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3335,52 +3363,67 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Carl Jansson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>104230292</v>
+        <v>104230305</v>
       </c>
       <c r="B28" t="n">
-        <v>92539</v>
+        <v>90932</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4365</v>
+        <v>1962</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3390,10 +3433,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>682837</v>
+        <v>683176</v>
       </c>
       <c r="R28" t="n">
-        <v>7101509</v>
+        <v>7101420</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3436,6 +3479,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3456,51 +3514,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126840195</v>
+        <v>104220674</v>
       </c>
       <c r="B29" t="n">
-        <v>79569</v>
+        <v>93213</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>2059</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gåsselmyren, Ång</t>
+          <t>Gåsselåsen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>683074</v>
+        <v>682951</v>
       </c>
       <c r="R29" t="n">
-        <v>7101349</v>
+        <v>7101573</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3524,12 +3579,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3538,33 +3593,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, kristina stenmarck, Jennica Andersson, Isac Enetjärn, Elke Blöhbaum, Lise Mortensen, Lisa Requin, Maria  Persbo , Vilhelm Kroon, Eleonor Johansson, Hedda Bring, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Lotta Ihse</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104230295</v>
+        <v>111835739</v>
       </c>
       <c r="B30" t="n">
-        <v>90283</v>
+        <v>91962</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3572,34 +3622,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gåsselliden, Bjurholm, Ång</t>
+          <t>Gåsselliden, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>683077</v>
+        <v>682686</v>
       </c>
       <c r="R30" t="n">
-        <v>7101491</v>
+        <v>7101482</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3626,12 +3676,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3642,45 +3692,30 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111835739</v>
+        <v>104230297</v>
       </c>
       <c r="B31" t="n">
-        <v>92727</v>
+        <v>93191</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3688,34 +3723,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2079</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gåsselliden, Ång</t>
+          <t>Gåsselliden, Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>682686</v>
+        <v>683086</v>
       </c>
       <c r="R31" t="n">
-        <v>7101482</v>
+        <v>7101479</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3742,12 +3777,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3762,61 +3797,61 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Carl Jansson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>104230272</v>
+        <v>104220701</v>
       </c>
       <c r="B32" t="n">
-        <v>96487</v>
+        <v>93197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Holmsjöbäcken, Bjurholm, Ång</t>
+          <t>Gåsselåsen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>684000</v>
+        <v>682908</v>
       </c>
       <c r="R32" t="n">
-        <v>7101275</v>
+        <v>7101264</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3863,26 +3898,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>104220695</v>
+        <v>104220702</v>
       </c>
       <c r="B33" t="n">
-        <v>91263</v>
+        <v>93197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3890,21 +3921,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3914,10 +3945,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>683957</v>
+        <v>682861</v>
       </c>
       <c r="R33" t="n">
-        <v>7101162</v>
+        <v>7101296</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3976,45 +4007,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>104230273</v>
+        <v>104220704</v>
       </c>
       <c r="B34" t="n">
-        <v>92519</v>
+        <v>93197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Holmsjöbäcken, Bjurholm, Ång</t>
+          <t>Gåsselåsen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>684028</v>
+        <v>682717</v>
       </c>
       <c r="R34" t="n">
-        <v>7101478</v>
+        <v>7101414</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,26 +4092,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126840196</v>
+        <v>104220705</v>
       </c>
       <c r="B35" t="n">
-        <v>78739</v>
+        <v>93197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4088,40 +4115,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gåsselmyren, Ång</t>
+          <t>Gåsselåsen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>683074</v>
+        <v>682741</v>
       </c>
       <c r="R35" t="n">
-        <v>7101349</v>
+        <v>7101486</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4145,12 +4169,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4159,37 +4183,32 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, kristina stenmarck, Jennica Andersson, Isac Enetjärn, Elke Blöhbaum, Lise Mortensen, Lisa Requin, Maria  Persbo , Vilhelm Kroon, Eleonor Johansson, Hedda Bring, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Lotta Ihse</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126839046</v>
+        <v>104220706</v>
       </c>
       <c r="B36" t="n">
-        <v>92535</v>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4213,17 +4232,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gåsselmyran, Ång</t>
+          <t>Gåsselåsen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>683036</v>
+        <v>683198</v>
       </c>
       <c r="R36" t="n">
-        <v>7101516</v>
+        <v>7101382</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4247,12 +4266,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4267,26 +4286,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>27860</v>
+        <v>104220708</v>
       </c>
       <c r="B37" t="n">
-        <v>56476</v>
+        <v>93197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4294,39 +4309,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100077</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Holmsjöbäcken, Ång</t>
+          <t>Gåsselåsen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>684081</v>
+        <v>683133</v>
       </c>
       <c r="R37" t="n">
-        <v>7101340</v>
+        <v>7101366</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4353,27 +4363,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2007-08-06</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2007-08-06</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Inventerare:Jonatan Borling, Eva-Britt Olofsson. Spillningsinnehåll:fisk o groda, under brofäste</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4388,26 +4383,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Via Jonas F Grahn</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Inventering av utter Västerbottens län 2005-2007</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>111835740</v>
+        <v>104230284</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>93197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4415,34 +4406,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gåsselliden, Ång</t>
+          <t>Gåsselliden, Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>682694</v>
+        <v>682854</v>
       </c>
       <c r="R38" t="n">
-        <v>7101498</v>
+        <v>7101295</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4469,12 +4460,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4489,26 +4480,26 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Carl Jansson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>104230297</v>
+        <v>104230307</v>
       </c>
       <c r="B39" t="n">
-        <v>92529</v>
+        <v>93197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4516,21 +4507,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4540,10 +4531,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>683086</v>
+        <v>683121</v>
       </c>
       <c r="R39" t="n">
-        <v>7101479</v>
+        <v>7101391</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4606,48 +4597,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>104220672</v>
+        <v>126839046</v>
       </c>
       <c r="B40" t="n">
-        <v>92519</v>
+        <v>93197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gåsselåsen, Ång</t>
+          <t>Gåsselmyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>682988</v>
+        <v>683036</v>
       </c>
       <c r="R40" t="n">
-        <v>7101559</v>
+        <v>7101516</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4671,12 +4662,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4691,57 +4682,61 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>104220669</v>
+        <v>104230292</v>
       </c>
       <c r="B41" t="n">
-        <v>91265</v>
+        <v>93201</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5442</v>
+        <v>4365</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gåsselåsen, Ång</t>
+          <t>Gåsselliden, Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>682822</v>
+        <v>682837</v>
       </c>
       <c r="R41" t="n">
-        <v>7101504</v>
+        <v>7101509</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4788,22 +4783,26 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Carl Jansson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>104230286</v>
+        <v>104220669</v>
       </c>
       <c r="B42" t="n">
-        <v>90283</v>
+        <v>91930</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4811,34 +4810,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1962</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gåsselliden, Bjurholm, Ång</t>
+          <t>Gåsselåsen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>682781</v>
+        <v>682822</v>
       </c>
       <c r="R42" t="n">
-        <v>7101323</v>
+        <v>7101504</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,44 +4881,25 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126840194</v>
+        <v>104230298</v>
       </c>
       <c r="B43" t="n">
-        <v>79598</v>
+        <v>93235</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4927,40 +4907,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gåsselmyren, Ång</t>
+          <t>Gåsselliden, Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>683075</v>
+        <v>683086</v>
       </c>
       <c r="R43" t="n">
-        <v>7101350</v>
+        <v>7101478</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4984,12 +4961,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4998,68 +4975,67 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, kristina stenmarck, Jennica Andersson, Isac Enetjärn, Elke Blöhbaum, Lise Mortensen, Lisa Requin, Maria  Persbo , Vilhelm Kroon, Eleonor Johansson, Hedda Bring, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>111835737</v>
+        <v>104220672</v>
       </c>
       <c r="B44" t="n">
-        <v>79569</v>
+        <v>93181</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6055</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gåsselliden, Ång</t>
+          <t>Gåsselåsen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>682659</v>
+        <v>682988</v>
       </c>
       <c r="R44" t="n">
-        <v>7101502</v>
+        <v>7101559</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5086,12 +5062,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5106,61 +5082,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>104220657</v>
+        <v>104230294</v>
       </c>
       <c r="B45" t="n">
-        <v>79569</v>
+        <v>93181</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6055</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gåsselåsen, Ång</t>
+          <t>Gåsselliden, Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>682900</v>
+        <v>683077</v>
       </c>
       <c r="R45" t="n">
-        <v>7101265</v>
+        <v>7101489</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5207,26 +5179,30 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Carl Jansson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126835885</v>
+        <v>104230303</v>
       </c>
       <c r="B46" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5250,14 +5226,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Gåsselliden, Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>683073</v>
+        <v>683151</v>
       </c>
       <c r="R46" t="n">
-        <v>7101301</v>
+        <v>7101435</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5284,12 +5260,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5300,21 +5276,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5324,52 +5285,56 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Carl Jansson, kristina stenmarck, Jennica Andersson, Isac Enetjärn, Beke Regelin, Elke Blöhbaum, Lise Mortensen, Lisa Requin, Peter Andersson, Maria  Persbo , Vilhelm Kroon, Eleonor Johansson, Hedda Bring, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Carl Jansson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126835882</v>
+        <v>111835740</v>
       </c>
       <c r="B47" t="n">
-        <v>78647</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Gåsselliden, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>683072</v>
+        <v>682694</v>
       </c>
       <c r="R47" t="n">
-        <v>7101304</v>
+        <v>7101498</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5396,12 +5361,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5412,76 +5377,65 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Carl Jansson, kristina stenmarck, Jennica Andersson, Isac Enetjärn, Beke Regelin, Elke Blöhbaum, Lise Mortensen, Lisa Requin, Peter Andersson, Maria  Persbo , Vilhelm Kroon, Eleonor Johansson, Hedda Bring, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>104230296</v>
+        <v>126835885</v>
       </c>
       <c r="B48" t="n">
-        <v>90283</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gåsselliden, Bjurholm, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>683082</v>
+        <v>683073</v>
       </c>
       <c r="R48" t="n">
-        <v>7101488</v>
+        <v>7101301</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5508,12 +5462,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5548,59 +5502,58 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Carl Jansson, kristina stenmarck, Jennica Andersson, Isac Enetjärn, Beke Regelin, Elke Blöhbaum, Lise Mortensen, Lisa Requin, Peter Andersson, Maria  Persbo , Vilhelm Kroon, Eleonor Johansson, Hedda Bring, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>104220711</v>
+        <v>126840198</v>
       </c>
       <c r="B49" t="n">
-        <v>77929</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gåsselåsen, Ång</t>
+          <t>Gåsselmyren, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>684056</v>
+        <v>683072</v>
       </c>
       <c r="R49" t="n">
-        <v>7101315</v>
+        <v>7101302</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5624,12 +5577,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Många på tallstammarna</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5638,50 +5596,55 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Beke Regelin, Carl Jansson, kristina stenmarck, Jennica Andersson, Isac Enetjärn, Elke Blöhbaum, Lise Mortensen, Lisa Requin, Maria  Persbo , Vilhelm Kroon, Eleonor Johansson, Hedda Bring, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Lotta Ihse</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>104220670</v>
+        <v>104220714</v>
       </c>
       <c r="B50" t="n">
-        <v>92565</v>
+        <v>78730</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>232140</v>
+        <v>6437</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5691,10 +5654,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>682846</v>
+        <v>682901</v>
       </c>
       <c r="R50" t="n">
-        <v>7101291</v>
+        <v>7101266</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5753,10 +5716,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>55564612</v>
+        <v>104220715</v>
       </c>
       <c r="B51" t="n">
-        <v>91263</v>
+        <v>78730</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5764,34 +5727,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Djupbäcken 1, Ång</t>
+          <t>Gåsselåsen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>683999</v>
+        <v>682747</v>
       </c>
       <c r="R51" t="n">
-        <v>7101251</v>
+        <v>7101398</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5818,17 +5781,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2015-06-25</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2015-06-25</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Lite för liten bäck, ont om bra ved</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5843,26 +5801,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Skapanior Eftersök</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126840199</v>
+        <v>16846942</v>
       </c>
       <c r="B52" t="n">
-        <v>78647</v>
+        <v>79084</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5870,40 +5824,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gåsselmyren, Ång</t>
+          <t>Gåsselmyran, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>683074</v>
+        <v>683144</v>
       </c>
       <c r="R52" t="n">
-        <v>7101300</v>
+        <v>7101221</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5927,17 +5878,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2013-06-30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På gammal silverlåga med brandljud och kol på undersidan</t>
+          <t>2013-06-30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5946,68 +5892,77 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>brandhögstubbe tall</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, kristina stenmarck, Jennica Andersson, Isac Enetjärn, Elke Blöhbaum, Lise Mortensen, Lisa Requin, Maria  Persbo , Vilhelm Kroon, Eleonor Johansson, Hedda Bring, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Niina Sallmén, sofia nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>104220702</v>
+        <v>104230293</v>
       </c>
       <c r="B53" t="n">
-        <v>92535</v>
+        <v>79084</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gåsselåsen, Ång</t>
+          <t>Gåsselliden, Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>682861</v>
+        <v>683027</v>
       </c>
       <c r="R53" t="n">
-        <v>7101296</v>
+        <v>7101473</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6051,63 +6006,85 @@
       <c r="AG53" t="b">
         <v>0</v>
       </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Carl Jansson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>104220701</v>
+        <v>126840197</v>
       </c>
       <c r="B54" t="n">
-        <v>92535</v>
+        <v>79084</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gåsselåsen, Ång</t>
+          <t>Gåsselmyren, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>682908</v>
+        <v>683074</v>
       </c>
       <c r="R54" t="n">
-        <v>7101264</v>
+        <v>7101349</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6131,12 +6108,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6145,28 +6122,33 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Beke Regelin, Carl Jansson, kristina stenmarck, Jennica Andersson, Isac Enetjärn, Elke Blöhbaum, Lise Mortensen, Lisa Requin, Maria  Persbo , Vilhelm Kroon, Eleonor Johansson, Hedda Bring, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Lotta Ihse</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>104220662</v>
+        <v>126840194</v>
       </c>
       <c r="B55" t="n">
-        <v>90283</v>
+        <v>79946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6174,37 +6156,40 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gåsselåsen, Ång</t>
+          <t>Gåsselmyren, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>683114</v>
+        <v>683075</v>
       </c>
       <c r="R55" t="n">
-        <v>7101481</v>
+        <v>7101350</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6228,12 +6213,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6242,28 +6227,33 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
+          <t>Beke Regelin, Carl Jansson, kristina stenmarck, Jennica Andersson, Isac Enetjärn, Elke Blöhbaum, Lise Mortensen, Lisa Requin, Maria  Persbo , Vilhelm Kroon, Eleonor Johansson, Hedda Bring, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Lotta Ihse</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>104220663</v>
+        <v>104220712</v>
       </c>
       <c r="B56" t="n">
-        <v>90283</v>
+        <v>78334</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6271,21 +6261,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6295,10 +6285,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>683248</v>
+        <v>682902</v>
       </c>
       <c r="R56" t="n">
-        <v>7101390</v>
+        <v>7101266</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6357,10 +6347,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>104230298</v>
+        <v>126835888</v>
       </c>
       <c r="B57" t="n">
-        <v>92571</v>
+        <v>5495</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6368,34 +6358,43 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5966</v>
+        <v>101410</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gåsselliden, Bjurholm, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>683086</v>
+        <v>682943</v>
       </c>
       <c r="R57" t="n">
-        <v>7101478</v>
+        <v>7101457</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6422,12 +6421,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6438,6 +6437,21 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -6447,59 +6461,58 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Carl Jansson, kristina stenmarck, Jennica Andersson, Isac Enetjärn, Beke Regelin, Elke Blöhbaum, Lise Mortensen, Lisa Requin, Peter Andersson, Maria  Persbo , Vilhelm Kroon, Eleonor Johansson, Hedda Bring, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>104230287</v>
+        <v>126840196</v>
       </c>
       <c r="B58" t="n">
-        <v>92565</v>
+        <v>79085</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>232140</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gåsselliden, Bjurholm, Ång</t>
+          <t>Gåsselmyren, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>682780</v>
+        <v>683074</v>
       </c>
       <c r="R58" t="n">
-        <v>7101325</v>
+        <v>7101349</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6523,12 +6536,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6537,67 +6550,68 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström</t>
+          <t>Beke Regelin, Carl Jansson, kristina stenmarck, Jennica Andersson, Isac Enetjärn, Elke Blöhbaum, Lise Mortensen, Lisa Requin, Maria  Persbo , Vilhelm Kroon, Eleonor Johansson, Hedda Bring, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>104230284</v>
+        <v>104220657</v>
       </c>
       <c r="B59" t="n">
-        <v>92535</v>
+        <v>79917</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gåsselliden, Bjurholm, Ång</t>
+          <t>Gåsselåsen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>682854</v>
+        <v>682900</v>
       </c>
       <c r="R59" t="n">
-        <v>7101295</v>
+        <v>7101265</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6644,26 +6658,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>111835736</v>
+        <v>126840195</v>
       </c>
       <c r="B60" t="n">
-        <v>91259</v>
+        <v>79917</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6671,37 +6681,40 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1204</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gåsselliden, Ång</t>
+          <t>Gåsselmyren, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>682650</v>
+        <v>683074</v>
       </c>
       <c r="R60" t="n">
-        <v>7101507</v>
+        <v>7101349</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6725,12 +6738,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6739,76 +6752,68 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Beke Regelin, Carl Jansson, kristina stenmarck, Jennica Andersson, Isac Enetjärn, Elke Blöhbaum, Lise Mortensen, Lisa Requin, Maria  Persbo , Vilhelm Kroon, Eleonor Johansson, Hedda Bring, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126835888</v>
+        <v>104220670</v>
       </c>
       <c r="B61" t="n">
-        <v>5492</v>
+        <v>93228</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>101410</v>
+        <v>232140</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Gåsselåsen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>682943</v>
+        <v>682846</v>
       </c>
       <c r="R61" t="n">
-        <v>7101457</v>
+        <v>7101291</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6835,12 +6840,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6851,76 +6856,61 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Carl Jansson, kristina stenmarck, Jennica Andersson, Isac Enetjärn, Beke Regelin, Elke Blöhbaum, Lise Mortensen, Lisa Requin, Peter Andersson, Maria  Persbo , Vilhelm Kroon, Eleonor Johansson, Hedda Bring, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson</t>
+          <t>Isak Vahlström, Carl Jansson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>104220708</v>
+        <v>104230287</v>
       </c>
       <c r="B62" t="n">
-        <v>92535</v>
+        <v>93228</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gåsselåsen, Ång</t>
+          <t>Gåsselliden, Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>683133</v>
+        <v>682780</v>
       </c>
       <c r="R62" t="n">
-        <v>7101366</v>
+        <v>7101325</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6967,22 +6957,26 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Carl Jansson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>104230303</v>
+        <v>126835886</v>
       </c>
       <c r="B63" t="n">
-        <v>78980</v>
+        <v>79350</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6990,34 +6984,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>260591</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gåsselliden, Bjurholm, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>683151</v>
+        <v>683073</v>
       </c>
       <c r="R63" t="n">
-        <v>7101435</v>
+        <v>7101301</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7044,12 +7038,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7060,6 +7054,21 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7069,43 +7078,39 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Carl Jansson, kristina stenmarck, Jennica Andersson, Isac Enetjärn, Beke Regelin, Elke Blöhbaum, Lise Mortensen, Lisa Requin, Peter Andersson, Maria  Persbo , Vilhelm Kroon, Eleonor Johansson, Hedda Bring, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>104220673</v>
+        <v>104220694</v>
       </c>
       <c r="B64" t="n">
-        <v>92551</v>
+        <v>92083</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2059</v>
+        <v>1503</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7115,10 +7120,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>682597</v>
+        <v>683606</v>
       </c>
       <c r="R64" t="n">
-        <v>7101488</v>
+        <v>7101466</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7177,10 +7182,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>104230305</v>
+        <v>104220663</v>
       </c>
       <c r="B65" t="n">
-        <v>90283</v>
+        <v>90932</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7208,14 +7213,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Gåsselliden, Bjurholm, Ång</t>
+          <t>Gåsselåsen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>683176</v>
+        <v>683248</v>
       </c>
       <c r="R65" t="n">
-        <v>7101420</v>
+        <v>7101390</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7259,44 +7264,25 @@
       <c r="AG65" t="b">
         <v>0</v>
       </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>104230307</v>
+        <v>104230272</v>
       </c>
       <c r="B66" t="n">
-        <v>92535</v>
+        <v>97231</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7304,34 +7290,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Gåsselliden, Bjurholm, Ång</t>
+          <t>Holmsjöbäcken, Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>683121</v>
+        <v>684000</v>
       </c>
       <c r="R66" t="n">
-        <v>7101391</v>
+        <v>7101275</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7394,45 +7380,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>104220715</v>
+        <v>104230273</v>
       </c>
       <c r="B67" t="n">
-        <v>78386</v>
+        <v>93181</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6437</v>
+        <v>6055</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Gåsselåsen, Ång</t>
+          <t>Holmsjöbäcken, Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>682747</v>
+        <v>684028</v>
       </c>
       <c r="R67" t="n">
-        <v>7101398</v>
+        <v>7101478</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7479,44 +7465,48 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
+          <t>Carl Jansson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>104220712</v>
+        <v>104220698</v>
       </c>
       <c r="B68" t="n">
-        <v>77929</v>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7526,10 +7516,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>682902</v>
+        <v>683803</v>
       </c>
       <c r="R68" t="n">
-        <v>7101266</v>
+        <v>7101645</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7588,32 +7578,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>104220704</v>
+        <v>104220711</v>
       </c>
       <c r="B69" t="n">
-        <v>92535</v>
+        <v>78334</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7623,10 +7613,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>682717</v>
+        <v>684056</v>
       </c>
       <c r="R69" t="n">
-        <v>7101414</v>
+        <v>7101315</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7682,6 +7672,117 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>27860</v>
+      </c>
+      <c r="B70" t="n">
+        <v>56766</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100077</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Utter</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lutra lutra</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Holmsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>684081</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7101340</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2007-08-06</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2007-08-06</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Inventerare:Jonatan Borling, Eva-Britt Olofsson. Spillningsinnehåll:fisk o groda, under brofäste</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Via Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Inventering av utter Västerbottens län 2005-2007</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
